--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-behandlungsepisode.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-behandlungsepisode.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:44:50+00:00</t>
+    <t>2026-09-11T15:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
